--- a/buckman/validation/2024/expected_outputs/Table_4_expected.xlsx
+++ b/buckman/validation/2024/expected_outputs/Table_4_expected.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 4 - Rio Grande, Otowi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,7 +29,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Aptos"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +58,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +66,29 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,8 +454,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -521,3331 +570,3719 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>2089</v>
       </c>
-      <c r="B2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="B2" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>0.025737</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>0.025725</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>0.02571</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>0.025696</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>0.025681</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3" t="n">
         <v>0.025668</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>0.02566</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="3" t="n">
         <v>0.02566</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="n">
         <v>0.025669</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="3" t="n">
         <v>0.025685</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="3" t="n">
         <v>0.025705</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="3" t="n">
         <v>0.025726</v>
       </c>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2090</v>
       </c>
-      <c r="B3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="B3" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.024342</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>0.024346</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>0.024348</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3" t="n">
         <v>0.024349</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="3" t="n">
         <v>0.02435</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>0.024351</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>0.024354</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="3" t="n">
         <v>0.024362</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="n">
         <v>0.024373</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="3" t="n">
         <v>0.02439</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="3" t="n">
         <v>0.024409</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="3" t="n">
         <v>0.024431</v>
       </c>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="2" t="n">
         <v>2091</v>
       </c>
-      <c r="B4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>0.013343</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>0.013353</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>0.013363</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="3" t="n">
         <v>0.013372</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="3" t="n">
         <v>0.013381</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="3" t="n">
         <v>0.01339</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>0.0134</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="3" t="n">
         <v>0.013411</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="n">
         <v>0.013424</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="3" t="n">
         <v>0.01344</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="3" t="n">
         <v>0.013459</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="3" t="n">
         <v>0.013479</v>
       </c>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="2" t="n">
         <v>2092</v>
       </c>
-      <c r="B5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="B5" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>0.007739</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>0.007749</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>0.007759</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3" t="n">
         <v>0.007768</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="3" t="n">
         <v>0.007778</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="3" t="n">
         <v>0.007787</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>0.007796</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="3" t="n">
         <v>0.007806</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="n">
         <v>0.007816999999999999</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="3" t="n">
         <v>0.007828999999999999</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="3" t="n">
         <v>0.007842999999999999</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="3" t="n">
         <v>0.007858</v>
       </c>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="2" t="n">
         <v>2093</v>
       </c>
-      <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="B6" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>0.004309</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>0.004314</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>0.00432</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3" t="n">
         <v>0.004325</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="3" t="n">
         <v>0.004331</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="3" t="n">
         <v>0.004336</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>0.004341</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="3" t="n">
         <v>0.004347</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3" t="n">
         <v>0.004352</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="3" t="n">
         <v>0.004359</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="3" t="n">
         <v>0.004366</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="3" t="n">
         <v>0.004374</v>
       </c>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="2" t="n">
         <v>2094</v>
       </c>
-      <c r="B7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="B7" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>0.001757</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>0.001758</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>0.00176</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="3" t="n">
         <v>0.001761</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="3" t="n">
         <v>0.001762</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>0.001763</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>0.001764</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="3" t="n">
         <v>0.001765</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3" t="n">
         <v>0.001766</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="3" t="n">
         <v>0.001767</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="3" t="n">
         <v>0.001769</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="3" t="n">
         <v>0.001771</v>
       </c>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="2" t="n">
         <v>2095</v>
       </c>
-      <c r="B8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="B8" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>0.001475</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>0.001476</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>0.001477</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3" t="n">
         <v>0.001478</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="3" t="n">
         <v>0.001479</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3" t="n">
         <v>0.001479</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>0.00148</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="3" t="n">
         <v>0.001481</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="n">
         <v>0.001481</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="3" t="n">
         <v>0.001482</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="3" t="n">
         <v>0.001483</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="3" t="n">
         <v>0.001485</v>
       </c>
-      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="2" t="n">
         <v>2096</v>
       </c>
-      <c r="B9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B9" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>0.001271</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3" t="n">
         <v>0.001272</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>0.001273</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="3" t="n">
         <v>0.001274</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="3" t="n">
         <v>0.001275</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="3" t="n">
         <v>0.001276</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>0.001277</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="3" t="n">
         <v>0.001277</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="3" t="n">
         <v>0.001278</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="3" t="n">
         <v>0.001279</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="3" t="n">
         <v>0.00128</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.001281</v>
       </c>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="2" t="n">
         <v>2097</v>
       </c>
-      <c r="B10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="B10" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>0.003938</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>0.003944</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>0.00395</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="3" t="n">
         <v>0.003955</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="3" t="n">
         <v>0.003961</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
         <v>0.003967</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>0.003972</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="3" t="n">
         <v>0.003978</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="3" t="n">
         <v>0.003984</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="3" t="n">
         <v>0.003991</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="3" t="n">
         <v>0.003997</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="3" t="n">
         <v>0.004005</v>
       </c>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="2" t="n">
         <v>2098</v>
       </c>
-      <c r="B11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="B11" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="3" t="n">
         <v>0.001343</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="3" t="n">
         <v>0.001344</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="3" t="n">
         <v>0.001345</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="3" t="n">
         <v>0.001347</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="3" t="n">
         <v>0.001348</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="3" t="n">
         <v>0.001349</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>0.00135</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="3" t="n">
         <v>0.001351</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="3" t="n">
         <v>0.001352</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="3" t="n">
         <v>0.001354</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="3" t="n">
         <v>0.001355</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="3" t="n">
         <v>0.001356</v>
       </c>
-      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="2" t="n">
         <v>2099</v>
       </c>
-      <c r="B12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="B12" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="3" t="n">
         <v>0.007659</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>0.007674</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3" t="n">
         <v>0.00769</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="3" t="n">
         <v>0.007705</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="3" t="n">
         <v>0.00772</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="3" t="n">
         <v>0.007735</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>0.00775</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="3" t="n">
         <v>0.007766</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="3" t="n">
         <v>0.007781</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="3" t="n">
         <v>0.007797</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" s="3" t="n">
         <v>0.007814</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="3" t="n">
         <v>0.007832</v>
       </c>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="2" t="n">
         <v>2100</v>
       </c>
-      <c r="B13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="B13" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="3" t="n">
         <v>0.000965</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="3" t="n">
         <v>0.000966</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="3" t="n">
         <v>0.000967</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="3" t="n">
         <v>0.000969</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="3" t="n">
         <v>0.0009700000000000001</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="3" t="n">
         <v>0.000971</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>0.000972</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="3" t="n">
         <v>0.000973</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="3" t="n">
         <v>0.000975</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="3" t="n">
         <v>0.000976</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" s="3" t="n">
         <v>0.000977</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13" s="3" t="n">
         <v>0.0009779999999999999</v>
       </c>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="2" t="n">
         <v>2101</v>
       </c>
-      <c r="B14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="B14" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="3" t="n">
         <v>0.005577</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="3" t="n">
         <v>0.005588</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="3" t="n">
         <v>0.005599</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="3" t="n">
         <v>0.00561</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="3" t="n">
         <v>0.005621</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="3" t="n">
         <v>0.005631</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3" t="n">
         <v>0.005642</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="3" t="n">
         <v>0.005652</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="3" t="n">
         <v>0.005663</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" s="3" t="n">
         <v>0.005674</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" s="3" t="n">
         <v>0.005685</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14" s="3" t="n">
         <v>0.005697</v>
       </c>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="2" t="n">
         <v>2102</v>
       </c>
-      <c r="B15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="B15" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="3" t="n">
         <v>0.0013</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="3" t="n">
         <v>0.001302</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="3" t="n">
         <v>0.001304</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="3" t="n">
         <v>0.001307</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="3" t="n">
         <v>0.001309</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="3" t="n">
         <v>0.001311</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>0.001313</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="3" t="n">
         <v>0.001315</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="3" t="n">
         <v>0.001317</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="3" t="n">
         <v>0.001319</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="3" t="n">
         <v>0.001321</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="3" t="n">
         <v>0.001323</v>
       </c>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="2" t="n">
         <v>2103</v>
       </c>
-      <c r="B16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="B16" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16" s="3" t="n">
         <v>0.0001</v>
       </c>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="2" t="n">
         <v>2104</v>
       </c>
-      <c r="B17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="B17" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="3" t="n">
         <v>0.003859</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="3" t="n">
         <v>0.003868</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="3" t="n">
         <v>0.003877</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="3" t="n">
         <v>0.003886</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="3" t="n">
         <v>0.003894</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="3" t="n">
         <v>0.003902</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3" t="n">
         <v>0.00391</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="3" t="n">
         <v>0.003918</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="3" t="n">
         <v>0.003926</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="3" t="n">
         <v>0.003934</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="3" t="n">
         <v>0.003942</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" s="3" t="n">
         <v>0.003951</v>
       </c>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="2" t="n">
         <v>2105</v>
       </c>
-      <c r="B18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="B18" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="3" t="n">
         <v>0.004141</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="3" t="n">
         <v>0.004152</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="3" t="n">
         <v>0.004164</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="3" t="n">
         <v>0.004176</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="3" t="n">
         <v>0.004186</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="3" t="n">
         <v>0.004196</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>0.004205</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="3" t="n">
         <v>0.004215</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="3" t="n">
         <v>0.004224</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="3" t="n">
         <v>0.004233</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="3" t="n">
         <v>0.004244</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18" s="3" t="n">
         <v>0.004255</v>
       </c>
-      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="2" t="n">
         <v>2106</v>
       </c>
-      <c r="B19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="B19" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="3" t="n">
         <v>0.002922</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="3" t="n">
         <v>0.002931</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="3" t="n">
         <v>0.002941</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="3" t="n">
         <v>0.002949</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="3" t="n">
         <v>0.002957</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="3" t="n">
         <v>0.002964</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3" t="n">
         <v>0.002971</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="3" t="n">
         <v>0.002978</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="3" t="n">
         <v>0.002985</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="3" t="n">
         <v>0.002992</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19" s="3" t="n">
         <v>0.002999</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19" s="3" t="n">
         <v>0.003006</v>
       </c>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="2" t="n">
         <v>2107</v>
       </c>
-      <c r="B20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="B20" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="3" t="n">
         <v>0.000727</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="3" t="n">
         <v>0.000728</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="3" t="n">
         <v>0.000728</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="3" t="n">
         <v>0.000729</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="3" t="n">
         <v>0.00073</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="3" t="n">
         <v>0.000731</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3" t="n">
         <v>0.000731</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="3" t="n">
         <v>0.000732</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="3" t="n">
         <v>0.000733</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="3" t="n">
         <v>0.000733</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20" s="3" t="n">
         <v>0.000734</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20" s="3" t="n">
         <v>0.000735</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>above</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="2" t="n">
         <v>2108</v>
       </c>
-      <c r="B21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="B21" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="3" t="n">
         <v>0.000821</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="3" t="n">
         <v>0.000822</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="3" t="n">
         <v>0.000822</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="3" t="n">
         <v>0.0008229999999999999</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="3" t="n">
         <v>0.000824</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="3" t="n">
         <v>0.000824</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>0.000825</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="3" t="n">
         <v>0.000826</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="3" t="n">
         <v>0.000826</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="3" t="n">
         <v>0.000827</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="3" t="n">
         <v>0.000828</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21" s="3" t="n">
         <v>0.000829</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>above</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="2" t="n">
         <v>2109</v>
       </c>
-      <c r="B22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="B22" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="3" t="n">
         <v>0.0009840000000000001</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="3" t="n">
         <v>0.000985</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="3" t="n">
         <v>0.000985</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="3" t="n">
         <v>0.0009859999999999999</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="3" t="n">
         <v>0.0009859999999999999</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="3" t="n">
         <v>0.000987</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3" t="n">
         <v>0.000987</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="3" t="n">
         <v>0.0009879999999999999</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="3" t="n">
         <v>0.0009879999999999999</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="3" t="n">
         <v>0.0009890000000000001</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="3" t="n">
         <v>0.00099</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" s="3" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>above</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="2" t="n">
         <v>2110</v>
       </c>
-      <c r="B23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
+      <c r="B23" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="3" t="n">
         <v>0.001659</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="3" t="n">
         <v>0.001659</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="3" t="n">
         <v>0.00166</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="3" t="n">
         <v>0.001661</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="3" t="n">
         <v>0.001661</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="3" t="n">
         <v>0.001662</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="3" t="n">
         <v>0.001662</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="3" t="n">
         <v>0.001663</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="3" t="n">
         <v>0.001663</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" s="3" t="n">
         <v>0.001665</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23" s="3" t="n">
         <v>0.001666</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23" s="3" t="n">
         <v>0.001668</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>above</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="2" t="n">
         <v>2111</v>
       </c>
-      <c r="B24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="B24" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="3" t="n">
         <v>0.003061</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="3" t="n">
         <v>0.003061</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="3" t="n">
         <v>0.00306</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="3" t="n">
         <v>0.00306</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="3" t="n">
         <v>0.003059</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="3" t="n">
         <v>0.003058</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="3" t="n">
         <v>0.003057</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="3" t="n">
         <v>0.003058</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" s="3" t="n">
         <v>0.003059</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24" s="3" t="n">
         <v>0.003062</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24" s="3" t="n">
         <v>0.003067</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24" s="3" t="n">
         <v>0.003072</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>above</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="2" t="n">
         <v>2112</v>
       </c>
-      <c r="B25" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="B25" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="3" t="n">
         <v>0.004439</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="3" t="n">
         <v>0.004436</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="3" t="n">
         <v>0.004432</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="3" t="n">
         <v>0.004428</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="3" t="n">
         <v>0.004424</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25" s="3" t="n">
         <v>0.004421</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3" t="n">
         <v>0.004419</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25" s="3" t="n">
         <v>0.004422</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" s="3" t="n">
         <v>0.004429</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25" s="3" t="n">
         <v>0.004441</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25" s="3" t="n">
         <v>0.004455</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25" s="3" t="n">
         <v>0.004472</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>above</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="2" t="n">
         <v>2113</v>
       </c>
-      <c r="B26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="B26" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="3" t="n">
         <v>0.00608</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="3" t="n">
         <v>0.006072</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="3" t="n">
         <v>0.006063</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" s="3" t="n">
         <v>0.006053</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="3" t="n">
         <v>0.006043</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26" s="3" t="n">
         <v>0.006036</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3" t="n">
         <v>0.006031</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" s="3" t="n">
         <v>0.006034</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" s="3" t="n">
         <v>0.006044</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26" s="3" t="n">
         <v>0.006061</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26" s="3" t="n">
         <v>0.006082</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q26" s="3" t="n">
         <v>0.006106</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>above</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="2" t="n">
         <v>2114</v>
       </c>
-      <c r="B27" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="B27" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="3" t="n">
         <v>0.011237</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="3" t="n">
         <v>0.011212</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="3" t="n">
         <v>0.011183</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="3" t="n">
         <v>0.011156</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="3" t="n">
         <v>0.011133</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27" s="3" t="n">
         <v>0.011121</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="3" t="n">
         <v>0.011129</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="3" t="n">
         <v>0.011164</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" s="3" t="n">
         <v>0.011222</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27" s="3" t="n">
         <v>0.011296</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P27" s="3" t="n">
         <v>0.011368</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q27" s="3" t="n">
         <v>0.01143</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>above</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="2" t="n">
         <v>2115</v>
       </c>
-      <c r="B28" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
+      <c r="B28" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="3" t="n">
         <v>0.034328</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="3" t="n">
         <v>0.034263</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="3" t="n">
         <v>0.034195</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="3" t="n">
         <v>0.034132</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="3" t="n">
         <v>0.034081</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28" s="3" t="n">
         <v>0.034057</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="3" t="n">
         <v>0.034079</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="3" t="n">
         <v>0.03416</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" s="3" t="n">
         <v>0.03428</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28" s="3" t="n">
         <v>0.03442</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P28" s="3" t="n">
         <v>0.034538</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q28" s="3" t="n">
         <v>0.034621</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>above</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="2" t="n">
         <v>2116</v>
       </c>
-      <c r="B29" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="B29" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="3" t="n">
         <v>0.07697900000000001</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="3" t="n">
         <v>0.07678699999999999</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="3" t="n">
         <v>0.076586</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="3" t="n">
         <v>0.07641299999999999</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="3" t="n">
         <v>0.07629900000000001</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" s="3" t="n">
         <v>0.076283</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="3" t="n">
         <v>0.07643800000000001</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="3" t="n">
         <v>0.07675999999999999</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="3" t="n">
         <v>0.077109</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29" s="3" t="n">
         <v>0.077418</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P29" s="3" t="n">
         <v>0.07757699999999999</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q29" s="3" t="n">
         <v>0.077597</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>above</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="2" t="n">
         <v>2117</v>
       </c>
-      <c r="B30" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
+      <c r="B30" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="3" t="n">
         <v>0.066747</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="3" t="n">
         <v>0.066511</v>
       </c>
-      <c r="H30" t="n">
-        <v>0.066222</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="H30" s="3" t="n">
+        <v>0.066223</v>
+      </c>
+      <c r="I30" s="3" t="n">
         <v>0.06605800000000001</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="3" t="n">
         <v>0.06614299999999999</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="3" t="n">
         <v>0.066528</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="3" t="n">
         <v>0.067535</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="3" t="n">
         <v>0.06881</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" s="3" t="n">
         <v>0.069691</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30" s="3" t="n">
         <v>0.07025000000000001</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P30" s="3" t="n">
         <v>0.070212</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30" s="3" t="n">
         <v>0.069922</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="2" t="n">
         <v>2118</v>
       </c>
-      <c r="B31" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="B31" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="3" t="n">
         <v>0.088028</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" s="3" t="n">
         <v>0.087752</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="3" t="n">
         <v>0.08697000000000001</v>
       </c>
-      <c r="I31" t="n">
-        <v>0.08693099999999999</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="I31" s="3" t="n">
+        <v>0.086932</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>0.088045</v>
       </c>
-      <c r="K31" t="n">
-        <v>0.090214</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="K31" s="3" t="n">
+        <v>0.090215</v>
+      </c>
+      <c r="L31" s="3" t="n">
         <v>0.09515899999999999</v>
       </c>
-      <c r="M31" t="n">
-        <v>0.100157</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.10231</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0.103305</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="M31" s="3" t="n">
+        <v>0.100158</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.102311</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>0.103306</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>0.101723</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q31" s="3" t="n">
         <v>0.100089</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="2" t="n">
         <v>2119</v>
       </c>
-      <c r="B32" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="B32" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F32" t="n">
-        <v>0.40057</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.435608</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.397245</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.44224</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.527637</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.621314</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.8718590000000001</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.978504</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.88812</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.8571220000000001</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.687771</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.661365</v>
-      </c>
-      <c r="R32" t="inlineStr">
+      <c r="F32" s="3" t="n">
+        <v>0.400578</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.435614</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.397255</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0.442261</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.527644</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.621332</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.871883</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>0.978514</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0.888122</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>0.857134</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0.687779</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>0.661384</v>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="2" t="n">
         <v>2120</v>
       </c>
-      <c r="B33" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="n">
+      <c r="B33" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="3" t="n">
         <v>0.132101</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" s="3" t="n">
         <v>0.130919</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="3" t="n">
         <v>0.129637</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="3" t="n">
         <v>0.128657</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="3" t="n">
         <v>0.128267</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33" s="3" t="n">
         <v>0.130041</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="3" t="n">
         <v>0.132853</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="3" t="n">
         <v>0.136051</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" s="3" t="n">
         <v>0.137833</v>
       </c>
-      <c r="O33" t="n">
-        <v>0.138821</v>
-      </c>
-      <c r="P33" t="n">
+      <c r="O33" s="3" t="n">
+        <v>0.13882</v>
+      </c>
+      <c r="P33" s="3" t="n">
         <v>0.138634</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q33" s="3" t="n">
         <v>0.137391</v>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="2" t="n">
         <v>2121</v>
       </c>
-      <c r="B34" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="B34" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="3" t="n">
         <v>0.024393</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34" s="3" t="n">
         <v>0.024204</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="3" t="n">
         <v>0.024008</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="3" t="n">
         <v>0.023838</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" s="3" t="n">
         <v>0.023721</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34" s="3" t="n">
         <v>0.023765</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34" s="3" t="n">
         <v>0.024003</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" s="3" t="n">
         <v>0.024421</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" s="3" t="n">
         <v>0.024877</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O34" s="3" t="n">
         <v>0.025321</v>
       </c>
-      <c r="P34" t="n">
+      <c r="P34" s="3" t="n">
         <v>0.025648</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q34" s="3" t="n">
         <v>0.025837</v>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="2" t="n">
         <v>2122</v>
       </c>
-      <c r="B35" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="n">
+      <c r="B35" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="3" t="n">
         <v>0.105611</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" s="3" t="n">
         <v>0.104972</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="3" t="n">
         <v>0.104314</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" s="3" t="n">
         <v>0.103743</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" s="3" t="n">
         <v>0.103336</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35" s="3" t="n">
         <v>0.103464</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="3" t="n">
         <v>0.104034</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="3" t="n">
         <v>0.104966</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35" s="3" t="n">
         <v>0.105795</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" s="3" t="n">
         <v>0.106445</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P35" s="3" t="n">
         <v>0.10672</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q35" s="3" t="n">
         <v>0.106584</v>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="2" t="n">
         <v>2123</v>
       </c>
-      <c r="B36" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="n">
+      <c r="B36" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="3" t="n">
         <v>0.039616</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36" s="3" t="n">
         <v>0.039469</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="3" t="n">
         <v>0.039317</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" s="3" t="n">
         <v>0.039183</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="3" t="n">
         <v>0.039082</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36" s="3" t="n">
         <v>0.039083</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36" s="3" t="n">
         <v>0.03923</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36" s="3" t="n">
         <v>0.03953</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36" s="3" t="n">
         <v>0.039898</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O36" s="3" t="n">
         <v>0.040283</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P36" s="3" t="n">
         <v>0.040589</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q36" s="3" t="n">
         <v>0.040787</v>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="2" t="n">
         <v>2124</v>
       </c>
-      <c r="B37" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="B37" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="3" t="n">
         <v>0.021981</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37" s="3" t="n">
         <v>0.021941</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="3" t="n">
         <v>0.021895</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="3" t="n">
         <v>0.021851</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="3" t="n">
         <v>0.021812</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37" s="3" t="n">
         <v>0.021793</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37" s="3" t="n">
         <v>0.02181</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37" s="3" t="n">
         <v>0.021878</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" s="3" t="n">
         <v>0.021986</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37" s="3" t="n">
         <v>0.022124</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P37" s="3" t="n">
         <v>0.02226</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q37" s="3" t="n">
         <v>0.022379</v>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="2" t="n">
         <v>2125</v>
       </c>
-      <c r="B38" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="B38" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="3" t="n">
         <v>0.004189</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38" s="3" t="n">
         <v>0.004187</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="3" t="n">
         <v>0.004185</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="3" t="n">
         <v>0.004181</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" s="3" t="n">
         <v>0.004176</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K38" s="3" t="n">
         <v>0.004172</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38" s="3" t="n">
         <v>0.004169</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38" s="3" t="n">
         <v>0.004168</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38" s="3" t="n">
         <v>0.004171</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O38" s="3" t="n">
         <v>0.004178</v>
       </c>
-      <c r="P38" t="n">
+      <c r="P38" s="3" t="n">
         <v>0.004189</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q38" s="3" t="n">
         <v>0.004203</v>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="2" t="n">
         <v>2126</v>
       </c>
-      <c r="B39" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
+      <c r="B39" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="3" t="n">
         <v>0.010208</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" s="3" t="n">
         <v>0.010202</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="3" t="n">
         <v>0.010193</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="3" t="n">
         <v>0.010183</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" s="3" t="n">
         <v>0.010172</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39" s="3" t="n">
         <v>0.010163</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39" s="3" t="n">
         <v>0.010162</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" s="3" t="n">
         <v>0.010172</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39" s="3" t="n">
         <v>0.010195</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O39" s="3" t="n">
         <v>0.010232</v>
       </c>
-      <c r="P39" t="n">
+      <c r="P39" s="3" t="n">
         <v>0.010275</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q39" s="3" t="n">
         <v>0.010323</v>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="2" t="n">
         <v>2127</v>
       </c>
-      <c r="B40" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
+      <c r="B40" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="3" t="n">
         <v>0.005094</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" s="3" t="n">
         <v>0.005095</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="3" t="n">
         <v>0.005095</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="3" t="n">
         <v>0.005094</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" s="3" t="n">
         <v>0.005092</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K40" s="3" t="n">
         <v>0.00509</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40" s="3" t="n">
         <v>0.005089</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40" s="3" t="n">
         <v>0.00509</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40" s="3" t="n">
         <v>0.005095</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O40" s="3" t="n">
         <v>0.005105</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P40" s="3" t="n">
         <v>0.005118</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q40" s="3" t="n">
         <v>0.005134</v>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="2" t="n">
         <v>2128</v>
       </c>
-      <c r="B41" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
+      <c r="B41" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="3" t="n">
         <v>0.003129</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41" s="3" t="n">
         <v>0.00313</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="3" t="n">
         <v>0.003131</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="3" t="n">
         <v>0.003132</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" s="3" t="n">
         <v>0.003132</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K41" s="3" t="n">
         <v>0.003132</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L41" s="3" t="n">
         <v>0.003132</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M41" s="3" t="n">
         <v>0.003133</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N41" s="3" t="n">
         <v>0.003134</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O41" s="3" t="n">
         <v>0.003136</v>
       </c>
-      <c r="P41" t="n">
+      <c r="P41" s="3" t="n">
         <v>0.003139</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q41" s="3" t="n">
         <v>0.003144</v>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="2" t="n">
         <v>2129</v>
       </c>
-      <c r="B42" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="n">
+      <c r="B42" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="3" t="n">
         <v>0.001587</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42" s="3" t="n">
         <v>0.001588</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="3" t="n">
         <v>0.001589</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" s="3" t="n">
         <v>0.00159</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" s="3" t="n">
         <v>0.001591</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K42" s="3" t="n">
         <v>0.001592</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42" s="3" t="n">
         <v>0.001593</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M42" s="3" t="n">
         <v>0.001594</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N42" s="3" t="n">
         <v>0.001595</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O42" s="3" t="n">
         <v>0.001596</v>
       </c>
-      <c r="P42" t="n">
+      <c r="P42" s="3" t="n">
         <v>0.001597</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q42" s="3" t="n">
         <v>0.001599</v>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="2" t="n">
         <v>2130</v>
       </c>
-      <c r="B43" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="n">
+      <c r="B43" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="3" t="n">
         <v>0.002137</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" s="3" t="n">
         <v>0.00214</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="3" t="n">
         <v>0.002142</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="3" t="n">
         <v>0.002144</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="3" t="n">
         <v>0.002146</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K43" s="3" t="n">
         <v>0.002147</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L43" s="3" t="n">
         <v>0.002149</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M43" s="3" t="n">
         <v>0.00215</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N43" s="3" t="n">
         <v>0.002152</v>
       </c>
-      <c r="O43" t="n">
+      <c r="O43" s="3" t="n">
         <v>0.002154</v>
       </c>
-      <c r="P43" t="n">
+      <c r="P43" s="3" t="n">
         <v>0.002157</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q43" s="3" t="n">
         <v>0.002161</v>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="2" t="n">
         <v>2131</v>
       </c>
-      <c r="B44" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="n">
+      <c r="B44" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="3" t="n">
         <v>0.001596</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="3" t="n">
         <v>0.001598</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="3" t="n">
         <v>0.001601</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="3" t="n">
         <v>0.001603</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" s="3" t="n">
         <v>0.001605</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K44" s="3" t="n">
         <v>0.001606</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L44" s="3" t="n">
         <v>0.001608</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M44" s="3" t="n">
         <v>0.00161</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N44" s="3" t="n">
         <v>0.001612</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O44" s="3" t="n">
         <v>0.001614</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P44" s="3" t="n">
         <v>0.001616</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q44" s="3" t="n">
         <v>0.001618</v>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="2" t="n">
         <v>2132</v>
       </c>
-      <c r="B45" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
+      <c r="B45" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="O45" t="n">
+      <c r="O45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q45" s="3" t="n">
         <v>0.00055</v>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R45" s="2" t="inlineStr">
         <is>
           <t>below</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="2" t="n">
         <v>2135</v>
       </c>
-      <c r="B46" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B46" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>0  RI</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>O GRA</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>NDE</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>1.047852</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1.07989</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1.037807</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1.080417</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1.165747</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1.263834</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.524295</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1.642591</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1.559367</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.533147</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.363504</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.334607</v>
-      </c>
-      <c r="R46" t="inlineStr"/>
+      <c r="F46" s="3" t="n">
+        <v>1.04786</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1.079896</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>1.037818</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>1.080438</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>1.165755</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1.263853</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>1.524319</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>1.642601</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>1.559368</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>1.533159</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>1.363513</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>1.334627</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="2" t="n">
         <v>2133</v>
       </c>
-      <c r="B47" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="B47" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>0  R</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>POJOA</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>QUE</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="3" t="n">
         <v>0.083581</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" s="3" t="n">
         <v>0.083605</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="3" t="n">
         <v>0.08362700000000001</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" s="3" t="n">
         <v>0.083645</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" s="3" t="n">
         <v>0.083662</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K47" s="3" t="n">
         <v>0.08368</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L47" s="3" t="n">
         <v>0.083707</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M47" s="3" t="n">
         <v>0.083748</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N47" s="3" t="n">
         <v>0.083804</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O47" s="3" t="n">
         <v>0.083881</v>
       </c>
-      <c r="P47" t="n">
+      <c r="P47" s="3" t="n">
         <v>0.083967</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q47" s="3" t="n">
         <v>0.084062</v>
       </c>
-      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="2" t="n">
         <v>2137</v>
       </c>
-      <c r="B48" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="B48" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>0  LC</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>SPRI</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>NGS</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="3" t="n">
         <v>0.00503</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" s="3" t="n">
         <v>0.005052</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="3" t="n">
         <v>0.005076</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48" s="3" t="n">
         <v>0.005098</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" s="3" t="n">
         <v>0.005122</v>
       </c>
-      <c r="K48" t="n">
+      <c r="K48" s="3" t="n">
         <v>0.005144</v>
       </c>
-      <c r="L48" t="n">
+      <c r="L48" s="3" t="n">
         <v>0.005166</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M48" s="3" t="n">
         <v>0.005189</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N48" s="3" t="n">
         <v>0.005209</v>
       </c>
-      <c r="O48" t="n">
+      <c r="O48" s="3" t="n">
         <v>0.005231</v>
       </c>
-      <c r="P48" t="n">
+      <c r="P48" s="3" t="n">
         <v>0.005252</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q48" s="3" t="n">
         <v>0.005273</v>
       </c>
-      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="2" t="n">
         <v>2134</v>
       </c>
-      <c r="B49" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="B49" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>0   R</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>TESU</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>QUE</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="3" t="n">
         <v>0.028195</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" s="3" t="n">
         <v>0.028257</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="3" t="n">
         <v>0.028321</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49" s="3" t="n">
         <v>0.028381</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" s="3" t="n">
         <v>0.02844</v>
       </c>
-      <c r="K49" t="n">
+      <c r="K49" s="3" t="n">
         <v>0.028496</v>
       </c>
-      <c r="L49" t="n">
+      <c r="L49" s="3" t="n">
         <v>0.028552</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M49" s="3" t="n">
         <v>0.028607</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N49" s="3" t="n">
         <v>0.028662</v>
       </c>
-      <c r="O49" t="n">
+      <c r="O49" s="3" t="n">
         <v>0.02872</v>
       </c>
-      <c r="P49" t="n">
+      <c r="P49" s="3" t="n">
         <v>0.02878</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="Q49" s="3" t="n">
         <v>0.028846</v>
       </c>
-      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="2" t="n">
         <v>2136</v>
       </c>
-      <c r="B50" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C50" t="inlineStr">
+      <c r="B50" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>0  RI</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>V  TO</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>TAL</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1.159628</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.191752</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1.149755</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1.192442</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.277849</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1.37601</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1.636553</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.754946</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1.671833</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1.645748</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.476251</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1.447515</v>
-      </c>
-      <c r="R50" t="inlineStr"/>
+      <c r="F50" s="3" t="n">
+        <v>1.159637</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>1.191758</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>1.149766</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>1.192464</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>1.277857</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>1.376029</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>1.636577</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>1.754956</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>1.671834</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>1.64576</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>1.476259</v>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>1.447535</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>jan</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>feb</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>apr</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>may</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>jun</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>jul</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>aug</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>sep</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>oct</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>nov</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>dec</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>cfs</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K52" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L52" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M52" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N52" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="O52" t="n">
+      <c r="O52" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="P52" t="n">
+      <c r="P52" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="Q52" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Rio Grande above Otowi</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="n">
+      <c r="F53" s="4" t="n">
         <v>0.140315</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" s="4" t="n">
         <v>0.140025</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="4" t="n">
         <v>0.139714</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" s="4" t="n">
         <v>0.139441</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" s="4" t="n">
         <v>0.13924</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K53" s="4" t="n">
         <v>0.13918</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L53" s="4" t="n">
         <v>0.139358</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M53" s="4" t="n">
         <v>0.139807</v>
       </c>
-      <c r="N53" t="n">
+      <c r="N53" s="4" t="n">
         <v>0.140353</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O53" s="4" t="n">
         <v>0.140912</v>
       </c>
-      <c r="P53" t="n">
+      <c r="P53" s="4" t="n">
         <v>0.141305</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="Q53" s="4" t="n">
         <v>0.141521</v>
       </c>
-      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Rio Grande below Otowi</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="n">
-        <v>0.9075370000000001</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.9398660000000001</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.8980940000000001</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.9409780000000002</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1.026507</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1.124654</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1.384935</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1.502784</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1.419014</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1.392236</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1.222198</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1.193086</v>
-      </c>
-      <c r="R54" t="inlineStr"/>
+      <c r="F54" s="4" t="n">
+        <v>0.9075450000000002</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0.939872</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0.898105</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>0.9410000000000002</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>1.026514</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>1.124673</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>1.384959</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>1.502795000000001</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>1.419017</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>1.392248</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>1.222206</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>1.193105</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P55" s="5" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="R55" s="5" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Rio Grande above Otowi</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Above Otowi</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>8.62763305785124</v>
-      </c>
-      <c r="G56" t="n">
+      <c r="F56" s="6" t="n">
+        <v>8.627633057851241</v>
+      </c>
+      <c r="G56" s="6" t="n">
         <v>7.776595041322314</v>
       </c>
-      <c r="H56" t="n">
-        <v>8.590679008264463</v>
-      </c>
-      <c r="I56" t="n">
-        <v>8.297315702479336</v>
-      </c>
-      <c r="J56" t="n">
-        <v>8.561533884297519</v>
-      </c>
-      <c r="K56" t="n">
+      <c r="H56" s="6" t="n">
+        <v>8.590679008264464</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>8.297315702479338</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>8.561533884297521</v>
+      </c>
+      <c r="K56" s="6" t="n">
         <v>8.281785123966943</v>
       </c>
-      <c r="L56" t="n">
-        <v>8.568789421487603</v>
-      </c>
-      <c r="M56" t="n">
+      <c r="L56" s="6" t="n">
+        <v>8.568789421487605</v>
+      </c>
+      <c r="M56" s="6" t="n">
         <v>8.5963973553719</v>
       </c>
-      <c r="N56" t="n">
-        <v>8.351583471074381</v>
-      </c>
-      <c r="O56" t="n">
+      <c r="N56" s="6" t="n">
+        <v>8.351583471074379</v>
+      </c>
+      <c r="O56" s="6" t="n">
         <v>8.664341157024792</v>
       </c>
-      <c r="P56" t="n">
-        <v>8.408231404958677</v>
-      </c>
-      <c r="Q56" t="n">
+      <c r="P56" s="6" t="n">
+        <v>8.408231404958679</v>
+      </c>
+      <c r="Q56" s="6" t="n">
         <v>8.701787107438017</v>
       </c>
-      <c r="R56" t="n">
+      <c r="R56" s="7" t="n">
         <v>101.4266717355372</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Rio Grande below Otowi</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Below Otowi</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>55.80227504132232</v>
-      </c>
-      <c r="G57" t="n">
-        <v>52.19751669421488</v>
-      </c>
-      <c r="H57" t="n">
-        <v>55.2216476033058</v>
-      </c>
-      <c r="I57" t="n">
-        <v>55.99207933884299</v>
-      </c>
-      <c r="J57" t="n">
-        <v>63.11745520661157</v>
-      </c>
-      <c r="K57" t="n">
-        <v>66.9215603305785</v>
-      </c>
-      <c r="L57" t="n">
-        <v>85.15633388429754</v>
-      </c>
-      <c r="M57" t="n">
-        <v>92.40258644628101</v>
-      </c>
-      <c r="N57" t="n">
-        <v>84.43719669421488</v>
-      </c>
-      <c r="O57" t="n">
-        <v>85.60525487603306</v>
-      </c>
-      <c r="P57" t="n">
-        <v>72.72583140495868</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>73.35999867768592</v>
-      </c>
-      <c r="R57" t="n">
-        <v>842.9397361983471</v>
+      <c r="F57" s="6" t="n">
+        <v>55.80276694214877</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>52.19784991735537</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>55.22232396694215</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>55.99338842975207</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>63.11788561983472</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>66.92269090909089</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>85.15780958677686</v>
+      </c>
+      <c r="M57" s="6" t="n">
+        <v>92.40326280991739</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>84.43737520661159</v>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>85.60599272727271</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v>72.72630743801655</v>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v>73.36116694214876</v>
+      </c>
+      <c r="R57" s="7" t="n">
+        <v>842.9488204958678</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Total RG (sum)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="n">
-        <v>64.42990809917356</v>
-      </c>
-      <c r="G58" t="n">
-        <v>59.9741117355372</v>
-      </c>
-      <c r="H58" t="n">
-        <v>63.81232661157026</v>
-      </c>
-      <c r="I58" t="n">
-        <v>64.28939504132232</v>
-      </c>
-      <c r="J58" t="n">
-        <v>71.6789890909091</v>
-      </c>
-      <c r="K58" t="n">
-        <v>75.20334545454544</v>
-      </c>
-      <c r="L58" t="n">
-        <v>93.72512330578515</v>
-      </c>
-      <c r="M58" t="n">
-        <v>100.9989838016529</v>
-      </c>
-      <c r="N58" t="n">
-        <v>92.78878016528925</v>
-      </c>
-      <c r="O58" t="n">
-        <v>94.26959603305785</v>
-      </c>
-      <c r="P58" t="n">
-        <v>81.13406280991737</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>82.06178578512394</v>
-      </c>
-      <c r="R58" t="inlineStr">
+      <c r="F58" s="6" t="n">
+        <v>64.43040000000002</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>59.97444495867769</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>63.81300297520662</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>64.29070413223141</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>71.67941950413224</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>75.20447603305783</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>93.72659900826447</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>100.9996601652893</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>92.78895867768597</v>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>94.2703338842975</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v>81.13453884297523</v>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v>82.06295404958678</v>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
         <is>
           <t>check</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Total RG reported</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="n">
-        <v>64.42990809917355</v>
-      </c>
-      <c r="G59" t="n">
-        <v>59.97405619834711</v>
-      </c>
-      <c r="H59" t="n">
-        <v>63.81226512396694</v>
-      </c>
-      <c r="I59" t="n">
-        <v>64.28927603305786</v>
-      </c>
-      <c r="J59" t="n">
-        <v>71.6789890909091</v>
-      </c>
-      <c r="K59" t="n">
-        <v>75.20334545454544</v>
-      </c>
-      <c r="L59" t="n">
-        <v>93.72524628099175</v>
-      </c>
-      <c r="M59" t="n">
-        <v>100.9989838016529</v>
-      </c>
-      <c r="N59" t="n">
-        <v>92.78878016528924</v>
-      </c>
-      <c r="O59" t="n">
-        <v>94.26953454545455</v>
-      </c>
-      <c r="P59" t="n">
-        <v>81.13412231404959</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>82.06178578512397</v>
-      </c>
-      <c r="R59" t="inlineStr">
+      <c r="F59" s="6" t="n">
+        <v>64.43040000000001</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>59.97438942148759</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>63.81294148760329</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>64.29052561983471</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>71.67948099173553</v>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>75.20447603305784</v>
+      </c>
+      <c r="L59" s="6" t="n">
+        <v>93.72672198347108</v>
+      </c>
+      <c r="M59" s="6" t="n">
+        <v>100.999598677686</v>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>92.78883966942151</v>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>94.2702723966942</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v>81.13465785123967</v>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v>82.06301553719008</v>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
         <is>
           <t>check</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>3 wells closest to 
 Rio Grande:
 Buckman 1, 7, 8; Row 13, Column 11</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="n">
-        <v>24.63008925619835</v>
-      </c>
-      <c r="G60" t="n">
-        <v>24.19244429752066</v>
-      </c>
-      <c r="H60" t="n">
-        <v>24.42564297520661</v>
-      </c>
-      <c r="I60" t="n">
-        <v>26.31510743801653</v>
-      </c>
-      <c r="J60" t="n">
-        <v>32.44313454545455</v>
-      </c>
-      <c r="K60" t="n">
-        <v>36.97075041322314</v>
-      </c>
-      <c r="L60" t="n">
-        <v>53.60852033057851</v>
-      </c>
-      <c r="M60" t="n">
-        <v>60.16586578512396</v>
-      </c>
-      <c r="N60" t="n">
-        <v>52.84680991735537</v>
-      </c>
-      <c r="O60" t="n">
-        <v>52.70237752066117</v>
-      </c>
-      <c r="P60" t="n">
-        <v>40.92521652892562</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>40.66574876033057</v>
-      </c>
-      <c r="R60" t="n">
-        <v>469.891707768595</v>
+      <c r="F60" s="6" t="n">
+        <v>24.6305811570248</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>24.19277752066115</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>24.42625785123967</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>26.31635702479339</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>32.44356495867769</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>36.9718214876033</v>
+      </c>
+      <c r="L60" s="6" t="n">
+        <v>53.60999603305785</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>60.16648066115702</v>
+      </c>
+      <c r="N60" s="6" t="n">
+        <v>52.84692892561984</v>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>52.70311537190083</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v>40.92569256198347</v>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v>40.66691702479339</v>
+      </c>
+      <c r="R60" s="7" t="n">
+        <v>469.9004905785123</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>CROSS-CHECK (formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUMIF: above Otowi</t>
+        </is>
+      </c>
+      <c r="F63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",F$2:F$45)-F53</f>
+        <v/>
+      </c>
+      <c r="G63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",G$2:G$45)-G53</f>
+        <v/>
+      </c>
+      <c r="H63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",H$2:H$45)-H53</f>
+        <v/>
+      </c>
+      <c r="I63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",I$2:I$45)-I53</f>
+        <v/>
+      </c>
+      <c r="J63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",J$2:J$45)-J53</f>
+        <v/>
+      </c>
+      <c r="K63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",K$2:K$45)-K53</f>
+        <v/>
+      </c>
+      <c r="L63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",L$2:L$45)-L53</f>
+        <v/>
+      </c>
+      <c r="M63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",M$2:M$45)-M53</f>
+        <v/>
+      </c>
+      <c r="N63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",N$2:N$45)-N53</f>
+        <v/>
+      </c>
+      <c r="O63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",O$2:O$45)-O53</f>
+        <v/>
+      </c>
+      <c r="P63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",P$2:P$45)-P53</f>
+        <v/>
+      </c>
+      <c r="Q63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",Q$2:Q$45)-Q53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUMIF: below Otowi</t>
+        </is>
+      </c>
+      <c r="F64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",F$2:F$45)-F54</f>
+        <v/>
+      </c>
+      <c r="G64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",G$2:G$45)-G54</f>
+        <v/>
+      </c>
+      <c r="H64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",H$2:H$45)-H54</f>
+        <v/>
+      </c>
+      <c r="I64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",I$2:I$45)-I54</f>
+        <v/>
+      </c>
+      <c r="J64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",J$2:J$45)-J54</f>
+        <v/>
+      </c>
+      <c r="K64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",K$2:K$45)-K54</f>
+        <v/>
+      </c>
+      <c r="L64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",L$2:L$45)-L54</f>
+        <v/>
+      </c>
+      <c r="M64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",M$2:M$45)-M54</f>
+        <v/>
+      </c>
+      <c r="N64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",N$2:N$45)-N54</f>
+        <v/>
+      </c>
+      <c r="O64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",O$2:O$45)-O54</f>
+        <v/>
+      </c>
+      <c r="P64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",P$2:P$45)-P54</f>
+        <v/>
+      </c>
+      <c r="Q64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",Q$2:Q$45)-Q54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUM: above (rows 20-29)</t>
+        </is>
+      </c>
+      <c r="F65" s="11">
+        <f>SUM(F20:F29)-F53</f>
+        <v/>
+      </c>
+      <c r="G65" s="11">
+        <f>SUM(G20:G29)-G53</f>
+        <v/>
+      </c>
+      <c r="H65" s="11">
+        <f>SUM(H20:H29)-H53</f>
+        <v/>
+      </c>
+      <c r="I65" s="11">
+        <f>SUM(I20:I29)-I53</f>
+        <v/>
+      </c>
+      <c r="J65" s="11">
+        <f>SUM(J20:J29)-J53</f>
+        <v/>
+      </c>
+      <c r="K65" s="11">
+        <f>SUM(K20:K29)-K53</f>
+        <v/>
+      </c>
+      <c r="L65" s="11">
+        <f>SUM(L20:L29)-L53</f>
+        <v/>
+      </c>
+      <c r="M65" s="11">
+        <f>SUM(M20:M29)-M53</f>
+        <v/>
+      </c>
+      <c r="N65" s="11">
+        <f>SUM(N20:N29)-N53</f>
+        <v/>
+      </c>
+      <c r="O65" s="11">
+        <f>SUM(O20:O29)-O53</f>
+        <v/>
+      </c>
+      <c r="P65" s="11">
+        <f>SUM(P20:P29)-P53</f>
+        <v/>
+      </c>
+      <c r="Q65" s="11">
+        <f>SUM(Q20:Q29)-Q53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUM: below (rows 30-45)</t>
+        </is>
+      </c>
+      <c r="F66" s="11">
+        <f>SUM(F30:F45)-F54</f>
+        <v/>
+      </c>
+      <c r="G66" s="11">
+        <f>SUM(G30:G45)-G54</f>
+        <v/>
+      </c>
+      <c r="H66" s="11">
+        <f>SUM(H30:H45)-H54</f>
+        <v/>
+      </c>
+      <c r="I66" s="11">
+        <f>SUM(I30:I45)-I54</f>
+        <v/>
+      </c>
+      <c r="J66" s="11">
+        <f>SUM(J30:J45)-J54</f>
+        <v/>
+      </c>
+      <c r="K66" s="11">
+        <f>SUM(K30:K45)-K54</f>
+        <v/>
+      </c>
+      <c r="L66" s="11">
+        <f>SUM(L30:L45)-L54</f>
+        <v/>
+      </c>
+      <c r="M66" s="11">
+        <f>SUM(M30:M45)-M54</f>
+        <v/>
+      </c>
+      <c r="N66" s="11">
+        <f>SUM(N30:N45)-N54</f>
+        <v/>
+      </c>
+      <c r="O66" s="11">
+        <f>SUM(O30:O45)-O54</f>
+        <v/>
+      </c>
+      <c r="P66" s="11">
+        <f>SUM(P30:P45)-P54</f>
+        <v/>
+      </c>
+      <c r="Q66" s="11">
+        <f>SUM(Q30:Q45)-Q54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>AF check: above Otowi</t>
+        </is>
+      </c>
+      <c r="F67" s="11">
+        <f>F53*F52*86400/43560-F56</f>
+        <v/>
+      </c>
+      <c r="G67" s="11">
+        <f>G53*G52*86400/43560-G56</f>
+        <v/>
+      </c>
+      <c r="H67" s="11">
+        <f>H53*H52*86400/43560-H56</f>
+        <v/>
+      </c>
+      <c r="I67" s="11">
+        <f>I53*I52*86400/43560-I56</f>
+        <v/>
+      </c>
+      <c r="J67" s="11">
+        <f>J53*J52*86400/43560-J56</f>
+        <v/>
+      </c>
+      <c r="K67" s="11">
+        <f>K53*K52*86400/43560-K56</f>
+        <v/>
+      </c>
+      <c r="L67" s="11">
+        <f>L53*L52*86400/43560-L56</f>
+        <v/>
+      </c>
+      <c r="M67" s="11">
+        <f>M53*M52*86400/43560-M56</f>
+        <v/>
+      </c>
+      <c r="N67" s="11">
+        <f>N53*N52*86400/43560-N56</f>
+        <v/>
+      </c>
+      <c r="O67" s="11">
+        <f>O53*O52*86400/43560-O56</f>
+        <v/>
+      </c>
+      <c r="P67" s="11">
+        <f>P53*P52*86400/43560-P56</f>
+        <v/>
+      </c>
+      <c r="Q67" s="11">
+        <f>Q53*Q52*86400/43560-Q56</f>
+        <v/>
+      </c>
+      <c r="R67" s="11">
+        <f>SUM(F67:Q67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>AF check: below Otowi</t>
+        </is>
+      </c>
+      <c r="F68" s="11">
+        <f>F54*F52*86400/43560-F57</f>
+        <v/>
+      </c>
+      <c r="G68" s="11">
+        <f>G54*G52*86400/43560-G57</f>
+        <v/>
+      </c>
+      <c r="H68" s="11">
+        <f>H54*H52*86400/43560-H57</f>
+        <v/>
+      </c>
+      <c r="I68" s="11">
+        <f>I54*I52*86400/43560-I57</f>
+        <v/>
+      </c>
+      <c r="J68" s="11">
+        <f>J54*J52*86400/43560-J57</f>
+        <v/>
+      </c>
+      <c r="K68" s="11">
+        <f>K54*K52*86400/43560-K57</f>
+        <v/>
+      </c>
+      <c r="L68" s="11">
+        <f>L54*L52*86400/43560-L57</f>
+        <v/>
+      </c>
+      <c r="M68" s="11">
+        <f>M54*M52*86400/43560-M57</f>
+        <v/>
+      </c>
+      <c r="N68" s="11">
+        <f>N54*N52*86400/43560-N57</f>
+        <v/>
+      </c>
+      <c r="O68" s="11">
+        <f>O54*O52*86400/43560-O57</f>
+        <v/>
+      </c>
+      <c r="P68" s="11">
+        <f>P54*P52*86400/43560-P57</f>
+        <v/>
+      </c>
+      <c r="Q68" s="11">
+        <f>Q54*Q52*86400/43560-Q57</f>
+        <v/>
+      </c>
+      <c r="R68" s="11">
+        <f>SUM(F68:Q68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Total check: above+below−sum</t>
+        </is>
+      </c>
+      <c r="F69" s="11">
+        <f>F56+F57-F58</f>
+        <v/>
+      </c>
+      <c r="G69" s="11">
+        <f>G56+G57-G58</f>
+        <v/>
+      </c>
+      <c r="H69" s="11">
+        <f>H56+H57-H58</f>
+        <v/>
+      </c>
+      <c r="I69" s="11">
+        <f>I56+I57-I58</f>
+        <v/>
+      </c>
+      <c r="J69" s="11">
+        <f>J56+J57-J58</f>
+        <v/>
+      </c>
+      <c r="K69" s="11">
+        <f>K56+K57-K58</f>
+        <v/>
+      </c>
+      <c r="L69" s="11">
+        <f>L56+L57-L58</f>
+        <v/>
+      </c>
+      <c r="M69" s="11">
+        <f>M56+M57-M58</f>
+        <v/>
+      </c>
+      <c r="N69" s="11">
+        <f>N56+N57-N58</f>
+        <v/>
+      </c>
+      <c r="O69" s="11">
+        <f>O56+O57-O58</f>
+        <v/>
+      </c>
+      <c r="P69" s="11">
+        <f>P56+P57-P58</f>
+        <v/>
+      </c>
+      <c r="Q69" s="11">
+        <f>Q56+Q57-Q58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>RG reported check: sum−sfmodflx</t>
+        </is>
+      </c>
+      <c r="F70" s="11">
+        <f>F58-F59</f>
+        <v/>
+      </c>
+      <c r="G70" s="11">
+        <f>G58-G59</f>
+        <v/>
+      </c>
+      <c r="H70" s="11">
+        <f>H58-H59</f>
+        <v/>
+      </c>
+      <c r="I70" s="11">
+        <f>I58-I59</f>
+        <v/>
+      </c>
+      <c r="J70" s="11">
+        <f>J58-J59</f>
+        <v/>
+      </c>
+      <c r="K70" s="11">
+        <f>K58-K59</f>
+        <v/>
+      </c>
+      <c r="L70" s="11">
+        <f>L58-L59</f>
+        <v/>
+      </c>
+      <c r="M70" s="11">
+        <f>M58-M59</f>
+        <v/>
+      </c>
+      <c r="N70" s="11">
+        <f>N58-N59</f>
+        <v/>
+      </c>
+      <c r="O70" s="11">
+        <f>O58-O59</f>
+        <v/>
+      </c>
+      <c r="P70" s="11">
+        <f>P58-P59</f>
+        <v/>
+      </c>
+      <c r="Q70" s="11">
+        <f>Q58-Q59</f>
+        <v/>
       </c>
     </row>
   </sheetData>
